--- a/JuegosHistorico.xlsx
+++ b/JuegosHistorico.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D276"/>
+  <dimension ref="A1:D576"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3143,10 +3143,8 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>730</t>
-        </is>
+      <c r="A152" t="n">
+        <v>730</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -3163,10 +3161,8 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>3764200</t>
-        </is>
+      <c r="A153" t="n">
+        <v>3764200</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -3183,10 +3179,8 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>686060</t>
-        </is>
+      <c r="A154" t="n">
+        <v>686060</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -3203,10 +3197,8 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>578080</t>
-        </is>
+      <c r="A155" t="n">
+        <v>578080</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -3223,10 +3215,8 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>1808500</t>
-        </is>
+      <c r="A156" t="n">
+        <v>1808500</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -3243,10 +3233,8 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>359550</t>
-        </is>
+      <c r="A157" t="n">
+        <v>359550</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -3263,10 +3251,8 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>2183900</t>
-        </is>
+      <c r="A158" t="n">
+        <v>2183900</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -3283,10 +3269,8 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>252490</t>
-        </is>
+      <c r="A159" t="n">
+        <v>252490</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -3303,10 +3287,8 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
+      <c r="A160" t="n">
+        <v>570</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -3323,10 +3305,8 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>3564740</t>
-        </is>
+      <c r="A161" t="n">
+        <v>3564740</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -3343,10 +3323,8 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>1721470</t>
-        </is>
+      <c r="A162" t="n">
+        <v>1721470</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -3363,10 +3341,8 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>1973530</t>
-        </is>
+      <c r="A163" t="n">
+        <v>1973530</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -3383,10 +3359,8 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>582660</t>
-        </is>
+      <c r="A164" t="n">
+        <v>582660</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -3403,10 +3377,8 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>3241660</t>
-        </is>
+      <c r="A165" t="n">
+        <v>3241660</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -3423,10 +3395,8 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>3240220</t>
-        </is>
+      <c r="A166" t="n">
+        <v>3240220</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -3443,10 +3413,8 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>1203220</t>
-        </is>
+      <c r="A167" t="n">
+        <v>1203220</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -3463,10 +3431,8 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>1172470</t>
-        </is>
+      <c r="A168" t="n">
+        <v>1172470</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -3483,10 +3449,8 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>3405690</t>
-        </is>
+      <c r="A169" t="n">
+        <v>3405690</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -3503,10 +3467,8 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>1151340</t>
-        </is>
+      <c r="A170" t="n">
+        <v>1151340</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -3523,10 +3485,8 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>2698940</t>
-        </is>
+      <c r="A171" t="n">
+        <v>2698940</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -3543,10 +3503,8 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>1086940</t>
-        </is>
+      <c r="A172" t="n">
+        <v>1086940</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -3563,10 +3521,8 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>230410</t>
-        </is>
+      <c r="A173" t="n">
+        <v>230410</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -3583,10 +3539,8 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>381210</t>
-        </is>
+      <c r="A174" t="n">
+        <v>381210</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -3603,10 +3557,8 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>553850</t>
-        </is>
+      <c r="A175" t="n">
+        <v>553850</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -3623,10 +3575,8 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>2221490</t>
-        </is>
+      <c r="A176" t="n">
+        <v>2221490</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -3643,10 +3593,8 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>3472040</t>
-        </is>
+      <c r="A177" t="n">
+        <v>3472040</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -3663,10 +3611,8 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>227300</t>
-        </is>
+      <c r="A178" t="n">
+        <v>227300</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -3683,10 +3629,8 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>266410</t>
-        </is>
+      <c r="A179" t="n">
+        <v>266410</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -3703,10 +3647,8 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>1599340</t>
-        </is>
+      <c r="A180" t="n">
+        <v>1599340</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -3723,10 +3665,8 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>2141910</t>
-        </is>
+      <c r="A181" t="n">
+        <v>2141910</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -3743,10 +3683,8 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>3164500</t>
-        </is>
+      <c r="A182" t="n">
+        <v>3164500</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -3763,10 +3701,8 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>3527290</t>
-        </is>
+      <c r="A183" t="n">
+        <v>3527290</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -3783,10 +3719,8 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>4100940</t>
-        </is>
+      <c r="A184" t="n">
+        <v>4100940</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -3803,10 +3737,8 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>322170</t>
-        </is>
+      <c r="A185" t="n">
+        <v>322170</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -3823,10 +3755,8 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>431960</t>
-        </is>
+      <c r="A186" t="n">
+        <v>431960</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -3843,10 +3773,8 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>2537590</t>
-        </is>
+      <c r="A187" t="n">
+        <v>2537590</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -3863,10 +3791,8 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>2840770</t>
-        </is>
+      <c r="A188" t="n">
+        <v>2840770</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -3883,10 +3809,8 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>2767030</t>
-        </is>
+      <c r="A189" t="n">
+        <v>2767030</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -3903,10 +3827,8 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>2139460</t>
-        </is>
+      <c r="A190" t="n">
+        <v>2139460</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -3923,10 +3845,8 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>2536520</t>
-        </is>
+      <c r="A191" t="n">
+        <v>2536520</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -3943,10 +3863,8 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>2807960</t>
-        </is>
+      <c r="A192" t="n">
+        <v>2807960</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -3963,10 +3881,8 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>413150</t>
-        </is>
+      <c r="A193" t="n">
+        <v>413150</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -3983,10 +3899,8 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>2344520</t>
-        </is>
+      <c r="A194" t="n">
+        <v>2344520</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -4003,10 +3917,8 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>236390</t>
-        </is>
+      <c r="A195" t="n">
+        <v>236390</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -4023,10 +3935,8 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>3159330</t>
-        </is>
+      <c r="A196" t="n">
+        <v>3159330</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -4043,10 +3953,8 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>976730</t>
-        </is>
+      <c r="A197" t="n">
+        <v>976730</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -4063,10 +3971,8 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>2050650</t>
-        </is>
+      <c r="A198" t="n">
+        <v>2050650</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
@@ -4083,10 +3989,8 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>4025700</t>
-        </is>
+      <c r="A199" t="n">
+        <v>4025700</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -4103,10 +4007,8 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>648800</t>
-        </is>
+      <c r="A200" t="n">
+        <v>648800</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -4123,10 +4025,8 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>2399830</t>
-        </is>
+      <c r="A201" t="n">
+        <v>2399830</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
@@ -4143,10 +4043,8 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>1245620</t>
-        </is>
+      <c r="A202" t="n">
+        <v>1245620</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -4163,10 +4061,8 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>394360</t>
-        </is>
+      <c r="A203" t="n">
+        <v>394360</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -4183,10 +4079,8 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>1250410</t>
-        </is>
+      <c r="A204" t="n">
+        <v>1250410</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -4203,10 +4097,8 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>306130</t>
-        </is>
+      <c r="A205" t="n">
+        <v>306130</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -4223,10 +4115,8 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>3321460</t>
-        </is>
+      <c r="A206" t="n">
+        <v>3321460</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -4243,10 +4133,8 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>739630</t>
-        </is>
+      <c r="A207" t="n">
+        <v>739630</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -4263,10 +4151,8 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>3419520</t>
-        </is>
+      <c r="A208" t="n">
+        <v>3419520</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -4283,10 +4169,8 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>2073620</t>
-        </is>
+      <c r="A209" t="n">
+        <v>2073620</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -4303,10 +4187,8 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>1665460</t>
-        </is>
+      <c r="A210" t="n">
+        <v>1665460</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -4323,10 +4205,8 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>2057760</t>
-        </is>
+      <c r="A211" t="n">
+        <v>2057760</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -4343,10 +4223,8 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>3274580</t>
-        </is>
+      <c r="A212" t="n">
+        <v>3274580</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
@@ -4363,10 +4241,8 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>1371980</t>
-        </is>
+      <c r="A213" t="n">
+        <v>1371980</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
@@ -4383,10 +4259,8 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>753640</t>
-        </is>
+      <c r="A214" t="n">
+        <v>753640</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
@@ -4403,10 +4277,8 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>216150</t>
-        </is>
+      <c r="A215" t="n">
+        <v>216150</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
@@ -4423,10 +4295,8 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>1659040</t>
-        </is>
+      <c r="A216" t="n">
+        <v>1659040</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
@@ -4443,10 +4313,8 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>3065800</t>
-        </is>
+      <c r="A217" t="n">
+        <v>3065800</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -4463,10 +4331,8 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>3370870</t>
-        </is>
+      <c r="A218" t="n">
+        <v>3370870</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -4483,10 +4349,8 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>2694490</t>
-        </is>
+      <c r="A219" t="n">
+        <v>2694490</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -4503,10 +4367,8 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>3681010</t>
-        </is>
+      <c r="A220" t="n">
+        <v>3681010</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -4523,10 +4385,8 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>1631270</t>
-        </is>
+      <c r="A221" t="n">
+        <v>1631270</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -4543,10 +4403,8 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>2357570</t>
-        </is>
+      <c r="A222" t="n">
+        <v>2357570</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -4563,10 +4421,8 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>2129530</t>
-        </is>
+      <c r="A223" t="n">
+        <v>2129530</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -4583,10 +4439,8 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>2507950</t>
-        </is>
+      <c r="A224" t="n">
+        <v>2507950</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -4603,10 +4457,8 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>2483190</t>
-        </is>
+      <c r="A225" t="n">
+        <v>2483190</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -4623,10 +4475,8 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>1091500</t>
-        </is>
+      <c r="A226" t="n">
+        <v>1091500</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -4643,10 +4493,8 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>108600</t>
-        </is>
+      <c r="A227" t="n">
+        <v>108600</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -4663,10 +4511,8 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>2799860</t>
-        </is>
+      <c r="A228" t="n">
+        <v>2799860</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
@@ -4683,10 +4529,8 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>438100</t>
-        </is>
+      <c r="A229" t="n">
+        <v>438100</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
@@ -4703,10 +4547,8 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>1158310</t>
-        </is>
+      <c r="A230" t="n">
+        <v>1158310</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
@@ -4723,10 +4565,8 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>813780</t>
-        </is>
+      <c r="A231" t="n">
+        <v>813780</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -4743,10 +4583,8 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>1401590</t>
-        </is>
+      <c r="A232" t="n">
+        <v>1401590</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
@@ -4763,10 +4601,8 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>1551360</t>
-        </is>
+      <c r="A233" t="n">
+        <v>1551360</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
@@ -4783,10 +4619,8 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>2697000</t>
-        </is>
+      <c r="A234" t="n">
+        <v>2697000</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
@@ -4803,10 +4637,8 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>2592160</t>
-        </is>
+      <c r="A235" t="n">
+        <v>2592160</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
@@ -4823,10 +4655,8 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>1313140</t>
-        </is>
+      <c r="A236" t="n">
+        <v>1313140</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
@@ -4843,10 +4673,8 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>346110</t>
-        </is>
+      <c r="A237" t="n">
+        <v>346110</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
@@ -4863,10 +4691,8 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>3059520</t>
-        </is>
+      <c r="A238" t="n">
+        <v>3059520</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
@@ -4883,10 +4709,8 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>250900</t>
-        </is>
+      <c r="A239" t="n">
+        <v>250900</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
@@ -4903,10 +4727,8 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>1617400</t>
-        </is>
+      <c r="A240" t="n">
+        <v>1617400</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
@@ -4923,10 +4745,8 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>3513350</t>
-        </is>
+      <c r="A241" t="n">
+        <v>3513350</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
@@ -4943,10 +4763,8 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>2948190</t>
-        </is>
+      <c r="A242" t="n">
+        <v>2948190</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
@@ -4963,10 +4781,8 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>1812450</t>
-        </is>
+      <c r="A243" t="n">
+        <v>1812450</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
@@ -4983,10 +4799,8 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>427520</t>
-        </is>
+      <c r="A244" t="n">
+        <v>427520</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
@@ -5003,10 +4817,8 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>2842040</t>
-        </is>
+      <c r="A245" t="n">
+        <v>2842040</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
@@ -5023,10 +4835,8 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>552520</t>
-        </is>
+      <c r="A246" t="n">
+        <v>552520</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
@@ -5043,10 +4853,8 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>2246340</t>
-        </is>
+      <c r="A247" t="n">
+        <v>2246340</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
@@ -5063,10 +4871,8 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>3226450</t>
-        </is>
+      <c r="A248" t="n">
+        <v>3226450</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
@@ -5083,10 +4889,8 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>2397300</t>
-        </is>
+      <c r="A249" t="n">
+        <v>2397300</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
@@ -5103,10 +4907,8 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>371660</t>
-        </is>
+      <c r="A250" t="n">
+        <v>371660</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
@@ -5123,10 +4925,8 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>1790930</t>
-        </is>
+      <c r="A251" t="n">
+        <v>1790930</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
@@ -5143,10 +4943,8 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>767560</t>
-        </is>
+      <c r="A252" t="n">
+        <v>767560</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
@@ -5163,10 +4961,8 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>284160</t>
-        </is>
+      <c r="A253" t="n">
+        <v>284160</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
@@ -5183,10 +4979,8 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>311210</t>
-        </is>
+      <c r="A254" t="n">
+        <v>311210</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
@@ -5203,10 +4997,8 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>2001120</t>
-        </is>
+      <c r="A255" t="n">
+        <v>2001120</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
@@ -5223,10 +5015,8 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>4069520</t>
-        </is>
+      <c r="A256" t="n">
+        <v>4069520</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
@@ -5243,10 +5033,8 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>2300320</t>
-        </is>
+      <c r="A257" t="n">
+        <v>2300320</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
@@ -5263,10 +5051,8 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>1363080</t>
-        </is>
+      <c r="A258" t="n">
+        <v>1363080</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
@@ -5283,10 +5069,8 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>1326470</t>
-        </is>
+      <c r="A259" t="n">
+        <v>1326470</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
@@ -5303,10 +5087,8 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>1903340</t>
-        </is>
+      <c r="A260" t="n">
+        <v>1903340</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
@@ -5323,10 +5105,8 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>39210</t>
-        </is>
+      <c r="A261" t="n">
+        <v>39210</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
@@ -5343,10 +5123,8 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>2555190</t>
-        </is>
+      <c r="A262" t="n">
+        <v>2555190</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
@@ -5363,10 +5141,8 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>2294660</t>
-        </is>
+      <c r="A263" t="n">
+        <v>2294660</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
@@ -5383,10 +5159,8 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>3405340</t>
-        </is>
+      <c r="A264" t="n">
+        <v>3405340</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
@@ -5403,10 +5177,8 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>377160</t>
-        </is>
+      <c r="A265" t="n">
+        <v>377160</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
@@ -5423,10 +5195,8 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>281990</t>
-        </is>
+      <c r="A266" t="n">
+        <v>281990</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
@@ -5443,10 +5213,8 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>1623730</t>
-        </is>
+      <c r="A267" t="n">
+        <v>1623730</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
@@ -5463,10 +5231,8 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>2627260</t>
-        </is>
+      <c r="A268" t="n">
+        <v>2627260</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
@@ -5483,10 +5249,8 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>1407200</t>
-        </is>
+      <c r="A269" t="n">
+        <v>1407200</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
@@ -5503,10 +5267,8 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>2406770</t>
-        </is>
+      <c r="A270" t="n">
+        <v>2406770</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
@@ -5523,10 +5285,8 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>1284210</t>
-        </is>
+      <c r="A271" t="n">
+        <v>1284210</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
@@ -5543,10 +5303,8 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>3834090</t>
-        </is>
+      <c r="A272" t="n">
+        <v>3834090</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
@@ -5563,10 +5321,8 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>1621690</t>
-        </is>
+      <c r="A273" t="n">
+        <v>1621690</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
@@ -5583,10 +5339,8 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>883710</t>
-        </is>
+      <c r="A274" t="n">
+        <v>883710</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
@@ -5603,10 +5357,8 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>1159690</t>
-        </is>
+      <c r="A275" t="n">
+        <v>1159690</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
@@ -5623,10 +5375,8 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>949230</t>
-        </is>
+      <c r="A276" t="n">
+        <v>949230</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
@@ -5640,6 +5390,5656 @@
       </c>
       <c r="D276" s="1" t="n">
         <v>46086.43083333333</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>3764200</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Resident Evil Requiem</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>69,99</t>
+        </is>
+      </c>
+      <c r="D277" s="1" t="n">
+        <v>46086.4978125</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>730</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Counter-Strike 2</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D278" s="1" t="n">
+        <v>46086.4978125</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>686060</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Mewgenics</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>28,99</t>
+        </is>
+      </c>
+      <c r="D279" s="1" t="n">
+        <v>46086.4978125</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>578080</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>PUBG: BATTLEGROUNDS</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D280" s="1" t="n">
+        <v>46086.4978125</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>1808500</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>ARC Raiders</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>39,99</t>
+        </is>
+      </c>
+      <c r="D281" s="1" t="n">
+        <v>46086.4978125</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>359550</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Tom Clancy's Rainbow Six Siege</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D282" s="1" t="n">
+        <v>46086.4978125</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>3564740</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Where Winds Meet</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D283" s="1" t="n">
+        <v>46086.4978125</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>2183900</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Warhammer 40,000: Space Marine 2</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>19,79</t>
+        </is>
+      </c>
+      <c r="D284" s="1" t="n">
+        <v>46086.4978125</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>570</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Dota 2</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D285" s="1" t="n">
+        <v>46086.4978125</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>252490</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Rust</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>39,99</t>
+        </is>
+      </c>
+      <c r="D286" s="1" t="n">
+        <v>46086.4978125</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>1973530</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Limbus Company</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D287" s="1" t="n">
+        <v>46086.4978125</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>1721470</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Poppy Playtime</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D288" s="1" t="n">
+        <v>46086.4978125</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>3241660</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>R.E.P.O.</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>6,64</t>
+        </is>
+      </c>
+      <c r="D289" s="1" t="n">
+        <v>46086.4978125</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>582660</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Black Desert</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>0,99</t>
+        </is>
+      </c>
+      <c r="D290" s="1" t="n">
+        <v>46086.4978125</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>230410</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Warframe</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D291" s="1" t="n">
+        <v>46086.4978125</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>1203220</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>NARAKA: BLADEPOINT</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D292" s="1" t="n">
+        <v>46086.4978125</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>3240220</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Grand Theft Auto V Enhanced</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>29,99</t>
+        </is>
+      </c>
+      <c r="D293" s="1" t="n">
+        <v>46086.4978125</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>1172470</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Apex Legends™</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D294" s="1" t="n">
+        <v>46086.4978125</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>3405690</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>EA SPORTS FC™ 26</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>48,00</t>
+        </is>
+      </c>
+      <c r="D295" s="1" t="n">
+        <v>46086.4978125</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>1151340</v>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Fallout 76</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>39,99</t>
+        </is>
+      </c>
+      <c r="D296" s="1" t="n">
+        <v>46086.4978125</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>2698940</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>The Crew Motorfest</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>6,99</t>
+        </is>
+      </c>
+      <c r="D297" s="1" t="n">
+        <v>46086.4978125</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>381210</v>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Dead by Daylight</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>19,99</t>
+        </is>
+      </c>
+      <c r="D298" s="1" t="n">
+        <v>46086.4978125</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>2221490</v>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Tom Clancy’s The Division® 2</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>2,99</t>
+        </is>
+      </c>
+      <c r="D299" s="1" t="n">
+        <v>46086.4978125</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>1086940</v>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Baldur's Gate 3</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>59,99</t>
+        </is>
+      </c>
+      <c r="D300" s="1" t="n">
+        <v>46086.4978125</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>553850</v>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>HELLDIVERS™ 2</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>39,99</t>
+        </is>
+      </c>
+      <c r="D301" s="1" t="n">
+        <v>46086.4978125</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>3764200</v>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Resident Evil Requiem</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>69,99</t>
+        </is>
+      </c>
+      <c r="D302" s="1" t="n">
+        <v>46086.49784722222</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>730</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Counter-Strike 2</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D303" s="1" t="n">
+        <v>46086.49784722222</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>686060</v>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Mewgenics</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>28,99</t>
+        </is>
+      </c>
+      <c r="D304" s="1" t="n">
+        <v>46086.49784722222</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>578080</v>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>PUBG: BATTLEGROUNDS</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D305" s="1" t="n">
+        <v>46086.49784722222</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>1808500</v>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>ARC Raiders</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>39,99</t>
+        </is>
+      </c>
+      <c r="D306" s="1" t="n">
+        <v>46086.49784722222</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>359550</v>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Tom Clancy's Rainbow Six Siege</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D307" s="1" t="n">
+        <v>46086.49784722222</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>3564740</v>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Where Winds Meet</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D308" s="1" t="n">
+        <v>46086.49784722222</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>2183900</v>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Warhammer 40,000: Space Marine 2</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>19,79</t>
+        </is>
+      </c>
+      <c r="D309" s="1" t="n">
+        <v>46086.49784722222</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>570</v>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Dota 2</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D310" s="1" t="n">
+        <v>46086.49784722222</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>252490</v>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Rust</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>39,99</t>
+        </is>
+      </c>
+      <c r="D311" s="1" t="n">
+        <v>46086.49784722222</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>1973530</v>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Limbus Company</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D312" s="1" t="n">
+        <v>46086.49784722222</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>1721470</v>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Poppy Playtime</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D313" s="1" t="n">
+        <v>46086.49784722222</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>3241660</v>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>R.E.P.O.</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>6,64</t>
+        </is>
+      </c>
+      <c r="D314" s="1" t="n">
+        <v>46086.49784722222</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>582660</v>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Black Desert</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>0,99</t>
+        </is>
+      </c>
+      <c r="D315" s="1" t="n">
+        <v>46086.49784722222</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>230410</v>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Warframe</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D316" s="1" t="n">
+        <v>46086.49784722222</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>1203220</v>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>NARAKA: BLADEPOINT</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D317" s="1" t="n">
+        <v>46086.49784722222</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>3240220</v>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Grand Theft Auto V Enhanced</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>29,99</t>
+        </is>
+      </c>
+      <c r="D318" s="1" t="n">
+        <v>46086.49784722222</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>1172470</v>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Apex Legends™</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D319" s="1" t="n">
+        <v>46086.49784722222</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>3405690</v>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>EA SPORTS FC™ 26</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>48,00</t>
+        </is>
+      </c>
+      <c r="D320" s="1" t="n">
+        <v>46086.49784722222</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>1151340</v>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Fallout 76</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>39,99</t>
+        </is>
+      </c>
+      <c r="D321" s="1" t="n">
+        <v>46086.49784722222</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>2698940</v>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>The Crew Motorfest</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>6,99</t>
+        </is>
+      </c>
+      <c r="D322" s="1" t="n">
+        <v>46086.49784722222</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>381210</v>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Dead by Daylight</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>19,99</t>
+        </is>
+      </c>
+      <c r="D323" s="1" t="n">
+        <v>46086.49784722222</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>2221490</v>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Tom Clancy’s The Division® 2</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>2,99</t>
+        </is>
+      </c>
+      <c r="D324" s="1" t="n">
+        <v>46086.49784722222</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>1086940</v>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Baldur's Gate 3</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>59,99</t>
+        </is>
+      </c>
+      <c r="D325" s="1" t="n">
+        <v>46086.49784722222</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>553850</v>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>HELLDIVERS™ 2</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>39,99</t>
+        </is>
+      </c>
+      <c r="D326" s="1" t="n">
+        <v>46086.49784722222</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>3764200</v>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Resident Evil Requiem</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>69,99</t>
+        </is>
+      </c>
+      <c r="D327" s="1" t="n">
+        <v>46086.49813657408</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>730</v>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Counter-Strike 2</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D328" s="1" t="n">
+        <v>46086.49813657408</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>686060</v>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Mewgenics</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>28,99</t>
+        </is>
+      </c>
+      <c r="D329" s="1" t="n">
+        <v>46086.49813657408</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>578080</v>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>PUBG: BATTLEGROUNDS</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D330" s="1" t="n">
+        <v>46086.49813657408</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>1808500</v>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>ARC Raiders</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>39,99</t>
+        </is>
+      </c>
+      <c r="D331" s="1" t="n">
+        <v>46086.49813657408</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>359550</v>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Tom Clancy's Rainbow Six Siege</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D332" s="1" t="n">
+        <v>46086.49813657408</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>3564740</v>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Where Winds Meet</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D333" s="1" t="n">
+        <v>46086.49813657408</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>2183900</v>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Warhammer 40,000: Space Marine 2</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>19,79</t>
+        </is>
+      </c>
+      <c r="D334" s="1" t="n">
+        <v>46086.49813657408</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>570</v>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Dota 2</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D335" s="1" t="n">
+        <v>46086.49813657408</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>252490</v>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Rust</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>39,99</t>
+        </is>
+      </c>
+      <c r="D336" s="1" t="n">
+        <v>46086.49813657408</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>1973530</v>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Limbus Company</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D337" s="1" t="n">
+        <v>46086.49813657408</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>1721470</v>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Poppy Playtime</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D338" s="1" t="n">
+        <v>46086.49813657408</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>3241660</v>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>R.E.P.O.</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>6,64</t>
+        </is>
+      </c>
+      <c r="D339" s="1" t="n">
+        <v>46086.49813657408</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>582660</v>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Black Desert</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>0,99</t>
+        </is>
+      </c>
+      <c r="D340" s="1" t="n">
+        <v>46086.49813657408</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>230410</v>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Warframe</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D341" s="1" t="n">
+        <v>46086.49813657408</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>1203220</v>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>NARAKA: BLADEPOINT</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D342" s="1" t="n">
+        <v>46086.49813657408</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>3240220</v>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Grand Theft Auto V Enhanced</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>29,99</t>
+        </is>
+      </c>
+      <c r="D343" s="1" t="n">
+        <v>46086.49813657408</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>1172470</v>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Apex Legends™</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D344" s="1" t="n">
+        <v>46086.49813657408</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>3405690</v>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>EA SPORTS FC™ 26</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>48,00</t>
+        </is>
+      </c>
+      <c r="D345" s="1" t="n">
+        <v>46086.49813657408</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>1151340</v>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Fallout 76</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>39,99</t>
+        </is>
+      </c>
+      <c r="D346" s="1" t="n">
+        <v>46086.49813657408</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>2698940</v>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>The Crew Motorfest</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>6,99</t>
+        </is>
+      </c>
+      <c r="D347" s="1" t="n">
+        <v>46086.49813657408</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>381210</v>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Dead by Daylight</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>19,99</t>
+        </is>
+      </c>
+      <c r="D348" s="1" t="n">
+        <v>46086.49813657408</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>2221490</v>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Tom Clancy’s The Division® 2</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>2,99</t>
+        </is>
+      </c>
+      <c r="D349" s="1" t="n">
+        <v>46086.49813657408</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>1086940</v>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Baldur's Gate 3</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>59,99</t>
+        </is>
+      </c>
+      <c r="D350" s="1" t="n">
+        <v>46086.49813657408</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>553850</v>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>HELLDIVERS™ 2</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>39,99</t>
+        </is>
+      </c>
+      <c r="D351" s="1" t="n">
+        <v>46086.49813657408</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>3472040</v>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>NBA 2K26</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>40,60</t>
+        </is>
+      </c>
+      <c r="D352" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>266410</v>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>iRacing</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>9,75</t>
+        </is>
+      </c>
+      <c r="D353" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>227300</v>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Euro Truck Simulator 2</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>19,99</t>
+        </is>
+      </c>
+      <c r="D354" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>1599340</v>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Lost Ark</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D355" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>1665460</v>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>eFootball™</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D356" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>2536520</v>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Diablo II: Resurrected – Infernal Edition</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>39,99</t>
+        </is>
+      </c>
+      <c r="D357" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>2344520</v>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Diablo® IV</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>49,99</t>
+        </is>
+      </c>
+      <c r="D358" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>2141910</v>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Magic: The Gathering Arena</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D359" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>322170</v>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Geometry Dash</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>2,49</t>
+        </is>
+      </c>
+      <c r="D360" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>431960</v>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Wallpaper Engine</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>3,99</t>
+        </is>
+      </c>
+      <c r="D361" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>4100940</v>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Poppy Playtime - Chapter 5</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>19,50</t>
+        </is>
+      </c>
+      <c r="D362" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>3164500</v>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Schedule I</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>19,50</t>
+        </is>
+      </c>
+      <c r="D363" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>2840770</v>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Avatar: Frontiers of Pandora™</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>19,49</t>
+        </is>
+      </c>
+      <c r="D364" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>2139460</v>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Once Human</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D365" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>3527290</v>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>PEAK</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>7,49</t>
+        </is>
+      </c>
+      <c r="D366" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>236390</v>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>War Thunder(VR Supported)</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D367" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>413150</v>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Stardew Valley</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>13,99</t>
+        </is>
+      </c>
+      <c r="D368" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>2767030</v>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Marvel Rivals</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D369" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>3159330</v>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Assassin’s Creed Shadows</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>34,99</t>
+        </is>
+      </c>
+      <c r="D370" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>2537590</v>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Microsoft Flight Simulator 2024</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>79,99</t>
+        </is>
+      </c>
+      <c r="D371" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>976730</v>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Halo: The Master Chief Collection</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>9,99</t>
+        </is>
+      </c>
+      <c r="D372" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>2807960</v>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Battlefield™ 6</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>69,99</t>
+        </is>
+      </c>
+      <c r="D373" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>2050650</v>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Resident Evil 4</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>39,99</t>
+        </is>
+      </c>
+      <c r="D374" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>648800</v>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Raft</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>19,99</t>
+        </is>
+      </c>
+      <c r="D375" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>2399830</v>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>ARK: Survival Ascended</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>44,99</t>
+        </is>
+      </c>
+      <c r="D376" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>2073620</v>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Arena Breakout: Infinite</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D377" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>4025700</v>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Heartopia</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D378" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>2694490</v>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Path of Exile 2</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>27,75</t>
+        </is>
+      </c>
+      <c r="D379" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>1245620</v>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>ELDEN RING</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>59,99</t>
+        </is>
+      </c>
+      <c r="D380" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>306130</v>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>The Elder Scrolls® Online</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>19,99</t>
+        </is>
+      </c>
+      <c r="D381" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>394360</v>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Hearts of Iron IV</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>49,99</t>
+        </is>
+      </c>
+      <c r="D382" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>739630</v>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Phasmophobia(VR Supported)</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>18,99</t>
+        </is>
+      </c>
+      <c r="D383" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>3321460</v>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Crimson Desert</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>69,99</t>
+        </is>
+      </c>
+      <c r="D384" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>1250410</v>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Microsoft Flight Simulator (2020) 40th Anniversary Edition(VR Supported)</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>24,49</t>
+        </is>
+      </c>
+      <c r="D385" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>3274580</v>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Anno 117: Pax Romana</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>44,99</t>
+        </is>
+      </c>
+      <c r="D386" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>2057760</v>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Esoteric Ebb</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>22,49</t>
+        </is>
+      </c>
+      <c r="D387" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>753640</v>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Outer Wilds</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>11,49</t>
+        </is>
+      </c>
+      <c r="D388" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>3419520</v>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Quarantine Zone: The Last Check</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>15,99</t>
+        </is>
+      </c>
+      <c r="D389" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>3065800</v>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>39,99</t>
+        </is>
+      </c>
+      <c r="D390" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>3370870</v>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Berry Bury Berry</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>7,79</t>
+        </is>
+      </c>
+      <c r="D391" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>813780</v>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Age of Empires II: Definitive Edition</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>32,99</t>
+        </is>
+      </c>
+      <c r="D392" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>2129530</v>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>REANIMAL</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>39,99</t>
+        </is>
+      </c>
+      <c r="D393" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>1659040</v>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>HITMAN World of Assassination</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>2,99</t>
+        </is>
+      </c>
+      <c r="D394" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>1371980</v>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>No Rest for the Wicked</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>39,99</t>
+        </is>
+      </c>
+      <c r="D395" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>2483190</v>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Forza Horizon 6</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>69,99</t>
+        </is>
+      </c>
+      <c r="D396" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>2357570</v>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Overwatch®</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D397" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>1091500</v>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Cyberpunk 2077</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>59,99</t>
+        </is>
+      </c>
+      <c r="D398" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>108600</v>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Project Zomboid</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>19,50</t>
+        </is>
+      </c>
+      <c r="D399" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>1631270</v>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>StarRupture</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>15,99</t>
+        </is>
+      </c>
+      <c r="D400" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>1449850</v>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Yu-Gi-Oh! Master Duel</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D401" s="1" t="n">
+        <v>46086.49814814814</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>1158310</v>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Crusader Kings III</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>49,99</t>
+        </is>
+      </c>
+      <c r="D402" s="1" t="n">
+        <v>46086.49815972222</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>250900</v>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>The Binding of Isaac: Rebirth</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>14,99</t>
+        </is>
+      </c>
+      <c r="D403" s="1" t="n">
+        <v>46086.49815972222</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>1313140</v>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Cult of the Lamb</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>22,99</t>
+        </is>
+      </c>
+      <c r="D404" s="1" t="n">
+        <v>46086.49815972222</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>2799860</v>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>INAZUMA ELEVEN: Victory Road</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>69,99</t>
+        </is>
+      </c>
+      <c r="D405" s="1" t="n">
+        <v>46086.49815972222</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>438100</v>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>VRChat(VR Supported)</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D406" s="1" t="n">
+        <v>46086.49815972222</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>3681010</v>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Nioh 3</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>79,99</t>
+        </is>
+      </c>
+      <c r="D407" s="1" t="n">
+        <v>46086.49815972222</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>3226450</v>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>iRacing Arcade</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>24,50</t>
+        </is>
+      </c>
+      <c r="D408" s="1" t="n">
+        <v>46086.49815972222</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>2697000</v>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>The Legend of Khiimori</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>29,99</t>
+        </is>
+      </c>
+      <c r="D409" s="1" t="n">
+        <v>46086.49815972222</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>1551360</v>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Forza Horizon 5</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>59,99</t>
+        </is>
+      </c>
+      <c r="D410" s="1" t="n">
+        <v>46086.49815972222</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>2300320</v>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Farming Simulator 25</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>29,99</t>
+        </is>
+      </c>
+      <c r="D411" s="1" t="n">
+        <v>46086.49815972222</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>552520</v>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Far Cry® 5</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>8,99</t>
+        </is>
+      </c>
+      <c r="D412" s="1" t="n">
+        <v>46086.49815972222</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>2592160</v>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>28,99</t>
+        </is>
+      </c>
+      <c r="D413" s="1" t="n">
+        <v>46086.49815972222</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>1617400</v>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>The Bazaar</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>15,99</t>
+        </is>
+      </c>
+      <c r="D414" s="1" t="n">
+        <v>46086.49815972222</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>1401590</v>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Disney Dreamlight Valley</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>39,99</t>
+        </is>
+      </c>
+      <c r="D415" s="1" t="n">
+        <v>46086.49815972222</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>2507950</v>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Delta Force</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D416" s="1" t="n">
+        <v>46086.49815972222</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>3059520</v>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>F1® 25(VR Supported)</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>59,99</t>
+        </is>
+      </c>
+      <c r="D417" s="1" t="n">
+        <v>46086.49815972222</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>2842040</v>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Star Wars Outlaws</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>20,99</t>
+        </is>
+      </c>
+      <c r="D418" s="1" t="n">
+        <v>46086.49815972222</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>767560</v>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>War Robots</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D419" s="1" t="n">
+        <v>46086.49815972222</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>2627260</v>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>NINJA GAIDEN 4</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>45,49</t>
+        </is>
+      </c>
+      <c r="D420" s="1" t="n">
+        <v>46086.49815972222</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>1812450</v>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Bellwright</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>28,99</t>
+        </is>
+      </c>
+      <c r="D421" s="1" t="n">
+        <v>46086.49815972222</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>2948190</v>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>World of Sea Battle</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D422" s="1" t="n">
+        <v>46086.49815972222</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>2358720</v>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Black Myth: Wukong</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>59,99</t>
+        </is>
+      </c>
+      <c r="D423" s="1" t="n">
+        <v>46086.49815972222</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>2246340</v>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Monster Hunter Wilds</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>69,99</t>
+        </is>
+      </c>
+      <c r="D424" s="1" t="n">
+        <v>46086.49815972222</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>2397300</v>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Half Sword</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>23,99</t>
+        </is>
+      </c>
+      <c r="D425" s="1" t="n">
+        <v>46086.49815972222</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>371660</v>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Far Cry® Primal</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>2,99</t>
+        </is>
+      </c>
+      <c r="D426" s="1" t="n">
+        <v>46086.49815972222</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>346110</v>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>ARK: Survival Evolved</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>14,79</t>
+        </is>
+      </c>
+      <c r="D427" s="1" t="n">
+        <v>46086.4981712963</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>281990</v>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Stellaris</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>39,99</t>
+        </is>
+      </c>
+      <c r="D428" s="1" t="n">
+        <v>46086.4981712963</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>2294660</v>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>The Quinfall</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>9,75</t>
+        </is>
+      </c>
+      <c r="D429" s="1" t="n">
+        <v>46086.4981712963</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>427520</v>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Factorio</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>32,00</t>
+        </is>
+      </c>
+      <c r="D430" s="1" t="n">
+        <v>46086.4981712963</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>1790930</v>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Crisol: Theater of Idols</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>17,49</t>
+        </is>
+      </c>
+      <c r="D431" s="1" t="n">
+        <v>46086.4981712963</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>3834090</v>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>YAPYAP</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>9,75</t>
+        </is>
+      </c>
+      <c r="D432" s="1" t="n">
+        <v>46086.4981712963</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="n">
+        <v>216150</v>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>MapleStory</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D433" s="1" t="n">
+        <v>46086.4981712963</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="n">
+        <v>949230</v>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Cities: Skylines II</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>49,99</t>
+        </is>
+      </c>
+      <c r="D434" s="1" t="n">
+        <v>46086.4981712963</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="n">
+        <v>4069520</v>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Super Battle Golf</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>7,99</t>
+        </is>
+      </c>
+      <c r="D435" s="1" t="n">
+        <v>46086.4981712963</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="n">
+        <v>2001120</v>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Split Fiction</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>49,99</t>
+        </is>
+      </c>
+      <c r="D436" s="1" t="n">
+        <v>46086.4981712963</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="n">
+        <v>1222670</v>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>The Sims™ 4</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D437" s="1" t="n">
+        <v>46086.4981712963</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="n">
+        <v>284160</v>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>BeamNG.drive</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>22,50</t>
+        </is>
+      </c>
+      <c r="D438" s="1" t="n">
+        <v>46086.4981712963</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="n">
+        <v>1466060</v>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Tainted Grail: The Fall of Avalon</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>43,99</t>
+        </is>
+      </c>
+      <c r="D439" s="1" t="n">
+        <v>46086.4981712963</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="n">
+        <v>1771300</v>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Kingdom Come: Deliverance II</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>59,99</t>
+        </is>
+      </c>
+      <c r="D440" s="1" t="n">
+        <v>46086.4981712963</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="n">
+        <v>311210</v>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Call of Duty®: Black Ops III</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>59,99</t>
+        </is>
+      </c>
+      <c r="D441" s="1" t="n">
+        <v>46086.4981712963</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="n">
+        <v>3405340</v>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Megabonk</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>7,31</t>
+        </is>
+      </c>
+      <c r="D442" s="1" t="n">
+        <v>46086.4981712963</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="n">
+        <v>2651280</v>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Marvel's Spider-Man 2</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>59,99</t>
+        </is>
+      </c>
+      <c r="D443" s="1" t="n">
+        <v>46086.4981712963</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="n">
+        <v>2555190</v>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Poppy Playtime - Chapter 3</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>14,79</t>
+        </is>
+      </c>
+      <c r="D444" s="1" t="n">
+        <v>46086.4981712963</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="n">
+        <v>1903340</v>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Clair Obscur: Expedition 33</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>49,99</t>
+        </is>
+      </c>
+      <c r="D445" s="1" t="n">
+        <v>46086.4981712963</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="n">
+        <v>1142710</v>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Total War: WARHAMMER III</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>59,99</t>
+        </is>
+      </c>
+      <c r="D446" s="1" t="n">
+        <v>46086.4981712963</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="n">
+        <v>3513350</v>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Wuthering Waves</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D447" s="1" t="n">
+        <v>46086.4981712963</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="n">
+        <v>1326470</v>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Sons Of The Forest</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>28,99</t>
+        </is>
+      </c>
+      <c r="D448" s="1" t="n">
+        <v>46086.4981712963</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="n">
+        <v>1623730</v>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Palworld</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>28,99</t>
+        </is>
+      </c>
+      <c r="D449" s="1" t="n">
+        <v>46086.4981712963</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="n">
+        <v>39210</v>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>FINAL FANTASY XIV Online</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>9,99</t>
+        </is>
+      </c>
+      <c r="D450" s="1" t="n">
+        <v>46086.4981712963</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="n">
+        <v>1284210</v>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Guild Wars 2®</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D451" s="1" t="n">
+        <v>46086.4981712963</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>3764200</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Resident Evil Requiem</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>69,99</t>
+        </is>
+      </c>
+      <c r="D452" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Counter-Strike 2</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D453" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>686060</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Mewgenics</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>28,99</t>
+        </is>
+      </c>
+      <c r="D454" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>578080</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>PUBG: BATTLEGROUNDS</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D455" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>1808500</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>ARC Raiders</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>39,99</t>
+        </is>
+      </c>
+      <c r="D456" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>359550</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Tom Clancy's Rainbow Six Siege</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D457" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>3564740</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Where Winds Meet</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D458" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2183900</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Warhammer 40,000: Space Marine 2</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>19,79</t>
+        </is>
+      </c>
+      <c r="D459" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Dota 2</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D460" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>252490</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Rust</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>39,99</t>
+        </is>
+      </c>
+      <c r="D461" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>1973530</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Limbus Company</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D462" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>1721470</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Poppy Playtime</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D463" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>3241660</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>R.E.P.O.</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>6,64</t>
+        </is>
+      </c>
+      <c r="D464" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>582660</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Black Desert</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>0,99</t>
+        </is>
+      </c>
+      <c r="D465" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>230410</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Warframe</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D466" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>1203220</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>NARAKA: BLADEPOINT</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D467" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>3240220</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Grand Theft Auto V Enhanced</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>29,99</t>
+        </is>
+      </c>
+      <c r="D468" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>1172470</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Apex Legends™</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D469" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>3405690</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>EA SPORTS FC™ 26</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>48,00</t>
+        </is>
+      </c>
+      <c r="D470" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>1151340</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Fallout 76</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>39,99</t>
+        </is>
+      </c>
+      <c r="D471" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2698940</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>The Crew Motorfest</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>6,99</t>
+        </is>
+      </c>
+      <c r="D472" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>381210</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Dead by Daylight</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>19,99</t>
+        </is>
+      </c>
+      <c r="D473" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2221490</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Tom Clancy’s The Division® 2</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>2,99</t>
+        </is>
+      </c>
+      <c r="D474" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>1086940</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Baldur's Gate 3</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>59,99</t>
+        </is>
+      </c>
+      <c r="D475" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>553850</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>HELLDIVERS™ 2</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>39,99</t>
+        </is>
+      </c>
+      <c r="D476" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>3472040</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>NBA 2K26</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>40,60</t>
+        </is>
+      </c>
+      <c r="D477" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>266410</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>iRacing</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>9,75</t>
+        </is>
+      </c>
+      <c r="D478" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>227300</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Euro Truck Simulator 2</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>19,99</t>
+        </is>
+      </c>
+      <c r="D479" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>1599340</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Lost Ark</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D480" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>1665460</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>eFootball™</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D481" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2536520</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Diablo II: Resurrected – Infernal Edition</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>39,99</t>
+        </is>
+      </c>
+      <c r="D482" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2344520</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Diablo® IV</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>49,99</t>
+        </is>
+      </c>
+      <c r="D483" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2141910</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Magic: The Gathering Arena</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D484" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>322170</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Geometry Dash</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>2,49</t>
+        </is>
+      </c>
+      <c r="D485" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>431960</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Wallpaper Engine</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>3,99</t>
+        </is>
+      </c>
+      <c r="D486" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>4100940</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Poppy Playtime - Chapter 5</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>19,50</t>
+        </is>
+      </c>
+      <c r="D487" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>3164500</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Schedule I</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>19,50</t>
+        </is>
+      </c>
+      <c r="D488" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2840770</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Avatar: Frontiers of Pandora™</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>19,49</t>
+        </is>
+      </c>
+      <c r="D489" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2139460</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Once Human</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D490" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>3527290</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>PEAK</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>7,49</t>
+        </is>
+      </c>
+      <c r="D491" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>236390</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>War Thunder(VR Supported)</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D492" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>413150</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Stardew Valley</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>13,99</t>
+        </is>
+      </c>
+      <c r="D493" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2767030</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Marvel Rivals</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D494" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>3159330</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Assassin’s Creed Shadows</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>34,99</t>
+        </is>
+      </c>
+      <c r="D495" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2537590</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Microsoft Flight Simulator 2024</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>79,99</t>
+        </is>
+      </c>
+      <c r="D496" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>976730</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Halo: The Master Chief Collection</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>9,99</t>
+        </is>
+      </c>
+      <c r="D497" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2807960</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Battlefield™ 6</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>69,99</t>
+        </is>
+      </c>
+      <c r="D498" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2050650</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Resident Evil 4</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>39,99</t>
+        </is>
+      </c>
+      <c r="D499" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>648800</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Raft</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>19,99</t>
+        </is>
+      </c>
+      <c r="D500" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2399830</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>ARK: Survival Ascended</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>44,99</t>
+        </is>
+      </c>
+      <c r="D501" s="1" t="n">
+        <v>46086.49851851852</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2073620</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Arena Breakout: Infinite</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D502" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>4025700</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Heartopia</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D503" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2694490</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Path of Exile 2</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>27,75</t>
+        </is>
+      </c>
+      <c r="D504" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>1245620</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>ELDEN RING</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>59,99</t>
+        </is>
+      </c>
+      <c r="D505" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>306130</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>The Elder Scrolls® Online</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>19,99</t>
+        </is>
+      </c>
+      <c r="D506" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>394360</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Hearts of Iron IV</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>49,99</t>
+        </is>
+      </c>
+      <c r="D507" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>739630</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Phasmophobia(VR Supported)</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>18,99</t>
+        </is>
+      </c>
+      <c r="D508" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>3321460</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Crimson Desert</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>69,99</t>
+        </is>
+      </c>
+      <c r="D509" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>1250410</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Microsoft Flight Simulator (2020) 40th Anniversary Edition(VR Supported)</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>24,49</t>
+        </is>
+      </c>
+      <c r="D510" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>3274580</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Anno 117: Pax Romana</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>44,99</t>
+        </is>
+      </c>
+      <c r="D511" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2057760</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Esoteric Ebb</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>22,49</t>
+        </is>
+      </c>
+      <c r="D512" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>753640</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Outer Wilds</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>11,49</t>
+        </is>
+      </c>
+      <c r="D513" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>3419520</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Quarantine Zone: The Last Check</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>15,99</t>
+        </is>
+      </c>
+      <c r="D514" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>3065800</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>39,99</t>
+        </is>
+      </c>
+      <c r="D515" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>3370870</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Berry Bury Berry</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>7,79</t>
+        </is>
+      </c>
+      <c r="D516" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>813780</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Age of Empires II: Definitive Edition</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>32,99</t>
+        </is>
+      </c>
+      <c r="D517" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2129530</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>REANIMAL</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>39,99</t>
+        </is>
+      </c>
+      <c r="D518" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>1659040</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>HITMAN World of Assassination</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>2,99</t>
+        </is>
+      </c>
+      <c r="D519" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>1371980</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>No Rest for the Wicked</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>39,99</t>
+        </is>
+      </c>
+      <c r="D520" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2483190</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Forza Horizon 6</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>69,99</t>
+        </is>
+      </c>
+      <c r="D521" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2357570</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Overwatch®</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D522" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>1091500</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Cyberpunk 2077</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>59,99</t>
+        </is>
+      </c>
+      <c r="D523" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>108600</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Project Zomboid</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>19,50</t>
+        </is>
+      </c>
+      <c r="D524" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>1631270</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>StarRupture</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>15,99</t>
+        </is>
+      </c>
+      <c r="D525" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>1449850</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Yu-Gi-Oh! Master Duel</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D526" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>1158310</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Crusader Kings III</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>49,99</t>
+        </is>
+      </c>
+      <c r="D527" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>250900</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>The Binding of Isaac: Rebirth</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>14,99</t>
+        </is>
+      </c>
+      <c r="D528" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>1313140</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Cult of the Lamb</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>22,99</t>
+        </is>
+      </c>
+      <c r="D529" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2799860</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>INAZUMA ELEVEN: Victory Road</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>69,99</t>
+        </is>
+      </c>
+      <c r="D530" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>438100</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>VRChat(VR Supported)</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D531" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>3681010</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Nioh 3</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>79,99</t>
+        </is>
+      </c>
+      <c r="D532" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>3226450</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>iRacing Arcade</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>24,50</t>
+        </is>
+      </c>
+      <c r="D533" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2697000</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>The Legend of Khiimori</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>29,99</t>
+        </is>
+      </c>
+      <c r="D534" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>1551360</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Forza Horizon 5</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>59,99</t>
+        </is>
+      </c>
+      <c r="D535" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2300320</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Farming Simulator 25</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>29,99</t>
+        </is>
+      </c>
+      <c r="D536" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>552520</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Far Cry® 5</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>8,99</t>
+        </is>
+      </c>
+      <c r="D537" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2592160</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>28,99</t>
+        </is>
+      </c>
+      <c r="D538" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>1617400</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>The Bazaar</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>15,99</t>
+        </is>
+      </c>
+      <c r="D539" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>1401590</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Disney Dreamlight Valley</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>39,99</t>
+        </is>
+      </c>
+      <c r="D540" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2507950</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Delta Force</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D541" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>3059520</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>F1® 25(VR Supported)</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>59,99</t>
+        </is>
+      </c>
+      <c r="D542" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2842040</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Star Wars Outlaws</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>20,99</t>
+        </is>
+      </c>
+      <c r="D543" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>767560</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>War Robots</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D544" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2627260</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>NINJA GAIDEN 4</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>45,49</t>
+        </is>
+      </c>
+      <c r="D545" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>1812450</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Bellwright</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>28,99</t>
+        </is>
+      </c>
+      <c r="D546" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2948190</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>World of Sea Battle</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D547" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2358720</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Black Myth: Wukong</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>59,99</t>
+        </is>
+      </c>
+      <c r="D548" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2246340</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Monster Hunter Wilds</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>69,99</t>
+        </is>
+      </c>
+      <c r="D549" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2397300</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Half Sword</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>23,99</t>
+        </is>
+      </c>
+      <c r="D550" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>371660</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Far Cry® Primal</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>2,99</t>
+        </is>
+      </c>
+      <c r="D551" s="1" t="n">
+        <v>46086.49853009259</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>346110</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>ARK: Survival Evolved</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>14,79</t>
+        </is>
+      </c>
+      <c r="D552" s="1" t="n">
+        <v>46086.49854166667</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>281990</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Stellaris</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>39,99</t>
+        </is>
+      </c>
+      <c r="D553" s="1" t="n">
+        <v>46086.49854166667</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2294660</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>The Quinfall</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>9,75</t>
+        </is>
+      </c>
+      <c r="D554" s="1" t="n">
+        <v>46086.49854166667</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>427520</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Factorio</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>32,00</t>
+        </is>
+      </c>
+      <c r="D555" s="1" t="n">
+        <v>46086.49854166667</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>1790930</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Crisol: Theater of Idols</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>17,49</t>
+        </is>
+      </c>
+      <c r="D556" s="1" t="n">
+        <v>46086.49854166667</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>3834090</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>YAPYAP</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>9,75</t>
+        </is>
+      </c>
+      <c r="D557" s="1" t="n">
+        <v>46086.49854166667</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>216150</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>MapleStory</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D558" s="1" t="n">
+        <v>46086.49854166667</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>949230</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Cities: Skylines II</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>49,99</t>
+        </is>
+      </c>
+      <c r="D559" s="1" t="n">
+        <v>46086.49854166667</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>4069520</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Super Battle Golf</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>7,99</t>
+        </is>
+      </c>
+      <c r="D560" s="1" t="n">
+        <v>46086.49854166667</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2001120</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Split Fiction</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>49,99</t>
+        </is>
+      </c>
+      <c r="D561" s="1" t="n">
+        <v>46086.49854166667</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>1222670</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>The Sims™ 4</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D562" s="1" t="n">
+        <v>46086.49854166667</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>284160</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>BeamNG.drive</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>22,50</t>
+        </is>
+      </c>
+      <c r="D563" s="1" t="n">
+        <v>46086.49854166667</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>1466060</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Tainted Grail: The Fall of Avalon</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>43,99</t>
+        </is>
+      </c>
+      <c r="D564" s="1" t="n">
+        <v>46086.49854166667</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>1771300</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Kingdom Come: Deliverance II</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>59,99</t>
+        </is>
+      </c>
+      <c r="D565" s="1" t="n">
+        <v>46086.49854166667</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>311210</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Call of Duty®: Black Ops III</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>59,99</t>
+        </is>
+      </c>
+      <c r="D566" s="1" t="n">
+        <v>46086.49854166667</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>3405340</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Megabonk</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>7,31</t>
+        </is>
+      </c>
+      <c r="D567" s="1" t="n">
+        <v>46086.49854166667</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2651280</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Marvel's Spider-Man 2</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>59,99</t>
+        </is>
+      </c>
+      <c r="D568" s="1" t="n">
+        <v>46086.49854166667</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2555190</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Poppy Playtime - Chapter 3</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>14,79</t>
+        </is>
+      </c>
+      <c r="D569" s="1" t="n">
+        <v>46086.49854166667</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>1903340</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Clair Obscur: Expedition 33</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>49,99</t>
+        </is>
+      </c>
+      <c r="D570" s="1" t="n">
+        <v>46086.49854166667</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>1142710</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Total War: WARHAMMER III</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>59,99</t>
+        </is>
+      </c>
+      <c r="D571" s="1" t="n">
+        <v>46086.49854166667</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>3513350</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Wuthering Waves</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D572" s="1" t="n">
+        <v>46086.49854166667</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>1326470</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Sons Of The Forest</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>28,99</t>
+        </is>
+      </c>
+      <c r="D573" s="1" t="n">
+        <v>46086.49854166667</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>1623730</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Palworld</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>28,99</t>
+        </is>
+      </c>
+      <c r="D574" s="1" t="n">
+        <v>46086.49854166667</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>39210</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>FINAL FANTASY XIV Online</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>9,99</t>
+        </is>
+      </c>
+      <c r="D575" s="1" t="n">
+        <v>46086.49854166667</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>1284210</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Guild Wars 2®</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D576" s="1" t="n">
+        <v>46086.49854166667</v>
       </c>
     </row>
   </sheetData>
